--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
@@ -1016,7 +1016,7 @@
     <x:col min="2" max="8" width="10.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="2" spans="1:8" customFormat="1" ht="30.75" customHeight="1">
+    <x:row r="2" spans="1:8" ht="30.75" customHeight="1">
       <x:c r="B2" s="13" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1039,7 +1039,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:8" customFormat="1" ht="20.1" customHeight="1">
+    <x:row r="3" spans="1:8" ht="20.1" customHeight="1">
       <x:c r="B3" s="1" t="s">
         <x:v>7</x:v>
       </x:c>
@@ -1175,7 +1175,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="3" spans="1:6"/>
-    <x:row r="4" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
+    <x:row r="4" spans="1:6" ht="11.25" customHeight="1"/>
     <x:row r="5" spans="1:6"/>
     <x:row r="6" spans="1:6"/>
     <x:row r="7" spans="1:6"/>
@@ -1185,83 +1185,83 @@
     <x:row r="11" spans="1:6"/>
     <x:row r="12" spans="1:6"/>
     <x:row r="13" spans="1:6"/>
-    <x:row r="14" spans="1:6" customFormat="1" ht="12.75" customHeight="1"/>
-    <x:row r="29" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="30" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="42" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="43" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="50" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="65" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="72" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="73" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="87" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="95" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="107" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="130" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="139" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="146" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="157" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="169" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="180" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="181" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="183" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="193" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="203" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="210" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="211" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="218" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="224" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="227" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="228" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="231" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="235" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="236" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="239" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="240" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="243" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="249" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="250" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="256" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="257" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="264" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="268" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="269" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="274" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="275" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="278" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="279" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="281" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="300" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="303" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="304" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="308" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="315" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="318" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="319" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="321" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="322" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="326" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="327" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="329" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="330" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="334" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="338" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="339" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="343" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="344" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="346" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="349" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="350" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="352" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="353" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="355" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="356" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="358" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="359" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="361" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="362" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="367" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
-    <x:row r="370" spans="1:6" customFormat="1" ht="11.25" customHeight="1"/>
+    <x:row r="14" spans="1:6" ht="12.75" customHeight="1"/>
+    <x:row r="29" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="30" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="42" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="43" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="50" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="65" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="72" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="73" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="87" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="95" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="107" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="130" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="139" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="146" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="157" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="169" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="180" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="181" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="183" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="193" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="203" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="210" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="211" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="218" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="224" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="227" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="228" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="231" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="235" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="236" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="239" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="240" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="243" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="249" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="250" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="256" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="257" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="264" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="268" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="269" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="274" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="275" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="278" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="279" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="281" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="300" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="303" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="304" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="308" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="315" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="318" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="319" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="321" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="322" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="326" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="327" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="329" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="330" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="334" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="338" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="339" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="343" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="344" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="346" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="349" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="350" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="352" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="353" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="355" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="356" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="358" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="359" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="361" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="362" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="367" spans="1:6" ht="11.25" customHeight="1"/>
+    <x:row r="370" spans="1:6" ht="11.25" customHeight="1"/>
   </x:sheetData>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
@@ -1052,13 +1052,13 @@
       <x:c r="E3" s="16">
         <x:v>32289</x:v>
       </x:c>
-      <x:c r="F3" s="17" t="n">
+      <x:c r="F3" s="17">
         <x:v>134.85</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="n">
+      <x:c r="G3" s="18">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H3" s="17" t="n">
+      <x:c r="H3" s="17">
         <x:v>134.85</x:v>
       </x:c>
     </x:row>
@@ -1075,13 +1075,13 @@
       <x:c r="E4" s="16">
         <x:v>32343</x:v>
       </x:c>
-      <x:c r="F4" s="17" t="n">
+      <x:c r="F4" s="17">
         <x:v>20108</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="n">
+      <x:c r="G4" s="18">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H4" s="17" t="n">
+      <x:c r="H4" s="17">
         <x:v>20108</x:v>
       </x:c>
     </x:row>
@@ -1098,13 +1098,13 @@
       <x:c r="E5" s="16">
         <x:v>32382</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="n">
+      <x:c r="F5" s="17">
         <x:v>10152</x:v>
       </x:c>
-      <x:c r="G5" s="18" t="n">
+      <x:c r="G5" s="18">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H5" s="17" t="n">
+      <x:c r="H5" s="17">
         <x:v>10152</x:v>
       </x:c>
     </x:row>
@@ -1121,13 +1121,13 @@
       <x:c r="E6" s="16">
         <x:v>34261</x:v>
       </x:c>
-      <x:c r="F6" s="17" t="n">
+      <x:c r="F6" s="17">
         <x:v>1004.8</x:v>
       </x:c>
-      <x:c r="G6" s="18" t="n">
+      <x:c r="G6" s="18">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H6" s="17" t="n">
+      <x:c r="H6" s="17">
         <x:v>1004.8</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
+++ b/ClosedXML.Tests/Resource/Other/PivotTableReferenceFiles/PivotSubtotalsSource/input.xlsx
@@ -1174,17 +1174,7 @@
     <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="3" spans="1:6"/>
     <x:row r="4" spans="1:6" ht="11.25" customHeight="1"/>
-    <x:row r="5" spans="1:6"/>
-    <x:row r="6" spans="1:6"/>
-    <x:row r="7" spans="1:6"/>
-    <x:row r="8" spans="1:6"/>
-    <x:row r="9" spans="1:6"/>
-    <x:row r="10" spans="1:6"/>
-    <x:row r="11" spans="1:6"/>
-    <x:row r="12" spans="1:6"/>
-    <x:row r="13" spans="1:6"/>
     <x:row r="14" spans="1:6" ht="12.75" customHeight="1"/>
     <x:row r="29" spans="1:6" ht="11.25" customHeight="1"/>
     <x:row r="30" spans="1:6" ht="11.25" customHeight="1"/>
